--- a/5/search/FY5_Missile3_results/best_solution.xlsx
+++ b/5/search/FY5_Missile3_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B2" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>12237.29596043756</v>
+        <v>12054.8413143137</v>
       </c>
       <c r="F2" t="n">
-        <v>-503.109039363542</v>
+        <v>-699.1006730450845</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>12173.73729047402</v>
+        <v>11818.55164289213</v>
       </c>
       <c r="I2" t="n">
-        <v>-378.3681259771705</v>
+        <v>-373.8758413063556</v>
       </c>
       <c r="J2" t="n">
-        <v>1295.1</v>
+        <v>1255.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
